--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1375,6 +1375,1813 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134036820</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Namnlöstjärn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>598471</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7106618</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134039452</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>598299</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7106677</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134036815</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80343</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Namnlöstjärn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>598280</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7106713</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134039453</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>598314</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7106661</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134039454</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80439</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>598366</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7106639</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134039458</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91894</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>598655</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7106548</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134039460</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91945</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>598701</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7106534</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134039459</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99170</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>598681</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7106543</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134036821</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Namnlöstjärn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>598544</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7106581</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134039455</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>598368</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7106638</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134036824</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Namnlöstjärn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>598638</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7106561</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134039457</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99148</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>598464</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7106595</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134036822</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91951</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Namnlöstjärn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>598581</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7106568</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134036827</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91931</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Namnlöstjärn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>598765</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7106548</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134039456</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>598460</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7106597</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134036819</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80439</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Namnlöstjärn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>598378</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7106663</v>
+      </c>
+      <c r="S23" t="n">
+        <v>17</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -2620,57 +2620,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134039457</v>
+        <v>134036822</v>
       </c>
       <c r="B19" t="n">
-        <v>99148</v>
+        <v>91951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598464</v>
+        <v>598581</v>
       </c>
       <c r="R19" t="n">
-        <v>7106595</v>
+        <v>7106568</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2702,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2712,7 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,19 +2705,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2744,41 +2727,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036822</v>
+        <v>134039457</v>
       </c>
       <c r="B20" t="n">
-        <v>91951</v>
+        <v>99148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598581</v>
+        <v>598464</v>
       </c>
       <c r="R20" t="n">
-        <v>7106568</v>
+        <v>7106595</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2810,7 +2809,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2819,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,18 +2828,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -2620,41 +2620,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036822</v>
+        <v>134039457</v>
       </c>
       <c r="B19" t="n">
-        <v>91951</v>
+        <v>99148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598581</v>
+        <v>598464</v>
       </c>
       <c r="R19" t="n">
-        <v>7106568</v>
+        <v>7106595</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2686,7 +2702,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2712,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,18 +2721,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2727,57 +2744,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134039457</v>
+        <v>134036822</v>
       </c>
       <c r="B20" t="n">
-        <v>99148</v>
+        <v>91951</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598464</v>
+        <v>598581</v>
       </c>
       <c r="R20" t="n">
-        <v>7106595</v>
+        <v>7106568</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2809,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2819,7 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,19 +2829,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -1380,7 +1380,7 @@
         <v>134036820</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>134039452</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>134036815</v>
       </c>
       <c r="B10" t="n">
-        <v>80343</v>
+        <v>80357</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134039453</v>
+        <v>134039454</v>
       </c>
       <c r="B11" t="n">
-        <v>91927</v>
+        <v>80453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598314</v>
+        <v>598366</v>
       </c>
       <c r="R11" t="n">
-        <v>7106661</v>
+        <v>7106639</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134039454</v>
+        <v>134039453</v>
       </c>
       <c r="B12" t="n">
-        <v>80439</v>
+        <v>91943</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598366</v>
+        <v>598314</v>
       </c>
       <c r="R12" t="n">
-        <v>7106639</v>
+        <v>7106661</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,7 +1941,7 @@
         <v>134039458</v>
       </c>
       <c r="B13" t="n">
-        <v>91894</v>
+        <v>91910</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>134039460</v>
       </c>
       <c r="B14" t="n">
-        <v>91945</v>
+        <v>91961</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>134039459</v>
       </c>
       <c r="B15" t="n">
-        <v>99170</v>
+        <v>99190</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>134036821</v>
       </c>
       <c r="B16" t="n">
-        <v>57136</v>
+        <v>57143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>134039455</v>
       </c>
       <c r="B17" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>134036824</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,57 +2620,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134039457</v>
+        <v>134036822</v>
       </c>
       <c r="B19" t="n">
-        <v>99148</v>
+        <v>91967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598464</v>
+        <v>598581</v>
       </c>
       <c r="R19" t="n">
-        <v>7106595</v>
+        <v>7106568</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2702,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2712,7 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,19 +2705,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2744,41 +2727,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036822</v>
+        <v>134039457</v>
       </c>
       <c r="B20" t="n">
-        <v>91951</v>
+        <v>99168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598581</v>
+        <v>598464</v>
       </c>
       <c r="R20" t="n">
-        <v>7106568</v>
+        <v>7106595</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2810,7 +2809,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2819,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,18 +2828,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2854,7 +2854,7 @@
         <v>134036827</v>
       </c>
       <c r="B21" t="n">
-        <v>91931</v>
+        <v>91947</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>134039456</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>134036819</v>
       </c>
       <c r="B23" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -1380,7 +1380,7 @@
         <v>134036820</v>
       </c>
       <c r="B8" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>134039452</v>
       </c>
       <c r="B9" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>134036815</v>
       </c>
       <c r="B10" t="n">
-        <v>80357</v>
+        <v>80367</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>134039454</v>
       </c>
       <c r="B11" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>134039453</v>
       </c>
       <c r="B12" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,32 +1938,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134039458</v>
+        <v>134039460</v>
       </c>
       <c r="B13" t="n">
-        <v>91910</v>
+        <v>91971</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598655</v>
+        <v>598701</v>
       </c>
       <c r="R13" t="n">
-        <v>7106548</v>
+        <v>7106534</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134039460</v>
+        <v>134039458</v>
       </c>
       <c r="B14" t="n">
-        <v>91961</v>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598701</v>
+        <v>598655</v>
       </c>
       <c r="R14" t="n">
-        <v>7106534</v>
+        <v>7106548</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,7 +2163,7 @@
         <v>134039459</v>
       </c>
       <c r="B15" t="n">
-        <v>99190</v>
+        <v>99200</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134036821</v>
+        <v>134039455</v>
       </c>
       <c r="B16" t="n">
-        <v>57143</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,45 +2282,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598544</v>
+        <v>598368</v>
       </c>
       <c r="R16" t="n">
-        <v>7106581</v>
+        <v>7106638</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2351,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,12 +2366,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2390,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134039455</v>
+        <v>134036821</v>
       </c>
       <c r="B17" t="n">
-        <v>79348</v>
+        <v>57153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,37 +2393,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598368</v>
+        <v>598544</v>
       </c>
       <c r="R17" t="n">
-        <v>7106638</v>
+        <v>7106581</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,12 +2485,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2504,7 +2504,7 @@
         <v>134036824</v>
       </c>
       <c r="B18" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>134036822</v>
       </c>
       <c r="B19" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>134039457</v>
       </c>
       <c r="B20" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>134036827</v>
       </c>
       <c r="B21" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>134039456</v>
       </c>
       <c r="B22" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>134036819</v>
       </c>
       <c r="B23" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -1938,32 +1938,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134039460</v>
+        <v>134039458</v>
       </c>
       <c r="B13" t="n">
-        <v>91971</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598701</v>
+        <v>598655</v>
       </c>
       <c r="R13" t="n">
-        <v>7106534</v>
+        <v>7106548</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134039458</v>
+        <v>134039460</v>
       </c>
       <c r="B14" t="n">
-        <v>91920</v>
+        <v>91971</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598655</v>
+        <v>598701</v>
       </c>
       <c r="R14" t="n">
-        <v>7106548</v>
+        <v>7106534</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134039455</v>
+        <v>134036821</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>57153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,37 +2282,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598368</v>
+        <v>598544</v>
       </c>
       <c r="R16" t="n">
-        <v>7106638</v>
+        <v>7106581</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,12 +2374,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2382,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134036821</v>
+        <v>134039455</v>
       </c>
       <c r="B17" t="n">
-        <v>57153</v>
+        <v>79358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,45 +2401,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598544</v>
+        <v>598368</v>
       </c>
       <c r="R17" t="n">
-        <v>7106581</v>
+        <v>7106638</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,12 +2485,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2620,41 +2620,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036822</v>
+        <v>134039457</v>
       </c>
       <c r="B19" t="n">
-        <v>91977</v>
+        <v>99178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598581</v>
+        <v>598464</v>
       </c>
       <c r="R19" t="n">
-        <v>7106568</v>
+        <v>7106595</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2686,7 +2702,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2712,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,18 +2721,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2727,57 +2744,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134039457</v>
+        <v>134036822</v>
       </c>
       <c r="B20" t="n">
-        <v>99178</v>
+        <v>91977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598464</v>
+        <v>598581</v>
       </c>
       <c r="R20" t="n">
-        <v>7106595</v>
+        <v>7106568</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2809,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2819,7 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,19 +2829,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134039454</v>
+        <v>134039453</v>
       </c>
       <c r="B11" t="n">
-        <v>80473</v>
+        <v>91953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598366</v>
+        <v>598314</v>
       </c>
       <c r="R11" t="n">
-        <v>7106639</v>
+        <v>7106661</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134039453</v>
+        <v>134039454</v>
       </c>
       <c r="B12" t="n">
-        <v>91953</v>
+        <v>80473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598314</v>
+        <v>598366</v>
       </c>
       <c r="R12" t="n">
-        <v>7106661</v>
+        <v>7106639</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,32 +1938,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134039458</v>
+        <v>134039460</v>
       </c>
       <c r="B13" t="n">
-        <v>91920</v>
+        <v>91971</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598655</v>
+        <v>598701</v>
       </c>
       <c r="R13" t="n">
-        <v>7106548</v>
+        <v>7106534</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134039460</v>
+        <v>134039458</v>
       </c>
       <c r="B14" t="n">
-        <v>91971</v>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598701</v>
+        <v>598655</v>
       </c>
       <c r="R14" t="n">
-        <v>7106534</v>
+        <v>7106548</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2620,57 +2620,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134039457</v>
+        <v>134036822</v>
       </c>
       <c r="B19" t="n">
-        <v>99178</v>
+        <v>91977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598464</v>
+        <v>598581</v>
       </c>
       <c r="R19" t="n">
-        <v>7106595</v>
+        <v>7106568</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2702,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2712,7 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,19 +2705,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2744,41 +2727,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036822</v>
+        <v>134039457</v>
       </c>
       <c r="B20" t="n">
-        <v>91977</v>
+        <v>99178</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598581</v>
+        <v>598464</v>
       </c>
       <c r="R20" t="n">
-        <v>7106568</v>
+        <v>7106595</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2810,7 +2809,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2819,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,18 +2828,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2851,10 +2851,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134036827</v>
+        <v>134039456</v>
       </c>
       <c r="B21" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,34 +2862,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598765</v>
+        <v>598460</v>
       </c>
       <c r="R21" t="n">
-        <v>7106548</v>
+        <v>7106597</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2946,12 +2946,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2962,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134039456</v>
+        <v>134036827</v>
       </c>
       <c r="B22" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,34 +2973,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598460</v>
+        <v>598765</v>
       </c>
       <c r="R22" t="n">
-        <v>7106597</v>
+        <v>7106548</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,12 +3057,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -1496,7 +1496,7 @@
         <v>134039452</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>134036815</v>
       </c>
       <c r="B10" t="n">
-        <v>80367</v>
+        <v>80368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>134039453</v>
       </c>
       <c r="B11" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>134039454</v>
       </c>
       <c r="B12" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,32 +1938,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134039460</v>
+        <v>134039458</v>
       </c>
       <c r="B13" t="n">
-        <v>91971</v>
+        <v>91922</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598701</v>
+        <v>598655</v>
       </c>
       <c r="R13" t="n">
-        <v>7106534</v>
+        <v>7106548</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,32 +2049,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134039458</v>
+        <v>134039460</v>
       </c>
       <c r="B14" t="n">
-        <v>91920</v>
+        <v>91973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598655</v>
+        <v>598701</v>
       </c>
       <c r="R14" t="n">
-        <v>7106548</v>
+        <v>7106534</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,7 +2163,7 @@
         <v>134039459</v>
       </c>
       <c r="B15" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>134039455</v>
       </c>
       <c r="B17" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>134036822</v>
       </c>
       <c r="B19" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>134039457</v>
       </c>
       <c r="B20" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,10 +2851,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134039456</v>
+        <v>134036827</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>91959</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,34 +2862,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598460</v>
+        <v>598765</v>
       </c>
       <c r="R21" t="n">
-        <v>7106597</v>
+        <v>7106548</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2946,12 +2946,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2962,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134036827</v>
+        <v>134039456</v>
       </c>
       <c r="B22" t="n">
-        <v>91957</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,34 +2973,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598765</v>
+        <v>598460</v>
       </c>
       <c r="R22" t="n">
-        <v>7106548</v>
+        <v>7106597</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,12 +3057,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3076,7 +3076,7 @@
         <v>134036819</v>
       </c>
       <c r="B23" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134039453</v>
+        <v>134039454</v>
       </c>
       <c r="B11" t="n">
-        <v>91955</v>
+        <v>80474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598314</v>
+        <v>598366</v>
       </c>
       <c r="R11" t="n">
-        <v>7106661</v>
+        <v>7106639</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134039454</v>
+        <v>134039453</v>
       </c>
       <c r="B12" t="n">
-        <v>80474</v>
+        <v>91955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598366</v>
+        <v>598314</v>
       </c>
       <c r="R12" t="n">
-        <v>7106639</v>
+        <v>7106661</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134036821</v>
+        <v>134039455</v>
       </c>
       <c r="B16" t="n">
-        <v>57153</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,45 +2282,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598544</v>
+        <v>598368</v>
       </c>
       <c r="R16" t="n">
-        <v>7106581</v>
+        <v>7106638</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2351,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,12 +2366,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2390,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134039455</v>
+        <v>134036821</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>57153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,37 +2393,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598368</v>
+        <v>598544</v>
       </c>
       <c r="R17" t="n">
-        <v>7106638</v>
+        <v>7106581</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,12 +2485,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2851,10 +2851,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134036827</v>
+        <v>134039456</v>
       </c>
       <c r="B21" t="n">
-        <v>91959</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,34 +2862,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598765</v>
+        <v>598460</v>
       </c>
       <c r="R21" t="n">
-        <v>7106548</v>
+        <v>7106597</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2946,12 +2946,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2962,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134039456</v>
+        <v>134036827</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>91959</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,34 +2973,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598460</v>
+        <v>598765</v>
       </c>
       <c r="R22" t="n">
-        <v>7106597</v>
+        <v>7106548</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,12 +3057,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134039454</v>
+        <v>134039453</v>
       </c>
       <c r="B11" t="n">
-        <v>80474</v>
+        <v>91956</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598366</v>
+        <v>598314</v>
       </c>
       <c r="R11" t="n">
-        <v>7106639</v>
+        <v>7106661</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134039453</v>
+        <v>134039454</v>
       </c>
       <c r="B12" t="n">
-        <v>91956</v>
+        <v>80474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598314</v>
+        <v>598366</v>
       </c>
       <c r="R12" t="n">
-        <v>7106661</v>
+        <v>7106639</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2620,41 +2620,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036822</v>
+        <v>134039457</v>
       </c>
       <c r="B19" t="n">
-        <v>91980</v>
+        <v>99181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598581</v>
+        <v>598464</v>
       </c>
       <c r="R19" t="n">
-        <v>7106568</v>
+        <v>7106595</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2686,7 +2702,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2712,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,18 +2721,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2727,57 +2744,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134039457</v>
+        <v>134036822</v>
       </c>
       <c r="B20" t="n">
-        <v>99181</v>
+        <v>91980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598464</v>
+        <v>598581</v>
       </c>
       <c r="R20" t="n">
-        <v>7106595</v>
+        <v>7106568</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2809,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2819,7 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,19 +2829,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -1496,7 +1496,7 @@
         <v>134039452</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>134036815</v>
       </c>
       <c r="B10" t="n">
-        <v>80368</v>
+        <v>80375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134039453</v>
+        <v>134039454</v>
       </c>
       <c r="B11" t="n">
-        <v>91956</v>
+        <v>80481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598314</v>
+        <v>598366</v>
       </c>
       <c r="R11" t="n">
-        <v>7106661</v>
+        <v>7106639</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134039454</v>
+        <v>134039453</v>
       </c>
       <c r="B12" t="n">
-        <v>80474</v>
+        <v>91963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598366</v>
+        <v>598314</v>
       </c>
       <c r="R12" t="n">
-        <v>7106639</v>
+        <v>7106661</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,7 +1941,7 @@
         <v>134039458</v>
       </c>
       <c r="B13" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>134039460</v>
       </c>
       <c r="B14" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>134039459</v>
       </c>
       <c r="B15" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134036821</v>
+        <v>134039455</v>
       </c>
       <c r="B16" t="n">
-        <v>57153</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,45 +2282,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598544</v>
+        <v>598368</v>
       </c>
       <c r="R16" t="n">
-        <v>7106581</v>
+        <v>7106638</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2351,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,12 +2366,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2390,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134039455</v>
+        <v>134036821</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>57153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,37 +2393,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598368</v>
+        <v>598544</v>
       </c>
       <c r="R17" t="n">
-        <v>7106638</v>
+        <v>7106581</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,12 +2485,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2620,57 +2620,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134039457</v>
+        <v>134036822</v>
       </c>
       <c r="B19" t="n">
-        <v>99181</v>
+        <v>91987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598464</v>
+        <v>598581</v>
       </c>
       <c r="R19" t="n">
-        <v>7106595</v>
+        <v>7106568</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2702,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2712,7 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,19 +2705,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2744,41 +2727,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036822</v>
+        <v>134039457</v>
       </c>
       <c r="B20" t="n">
-        <v>91980</v>
+        <v>99188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598581</v>
+        <v>598464</v>
       </c>
       <c r="R20" t="n">
-        <v>7106568</v>
+        <v>7106595</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2810,7 +2809,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2819,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,18 +2828,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2851,10 +2851,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134039456</v>
+        <v>134036827</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>91967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,34 +2862,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598460</v>
+        <v>598765</v>
       </c>
       <c r="R21" t="n">
-        <v>7106597</v>
+        <v>7106548</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2946,12 +2946,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2962,10 +2962,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134036827</v>
+        <v>134039456</v>
       </c>
       <c r="B22" t="n">
-        <v>91960</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,34 +2973,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598765</v>
+        <v>598460</v>
       </c>
       <c r="R22" t="n">
-        <v>7106548</v>
+        <v>7106597</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,12 +3057,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3076,7 +3076,7 @@
         <v>134036819</v>
       </c>
       <c r="B23" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>7016231</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598685.7879172558</v>
+        <v>598686</v>
       </c>
       <c r="R2" t="n">
-        <v>7106515.852160064</v>
+        <v>7106516</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2013-07-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,50 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7016346</v>
+        <v>134036816</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörnoret (8400m SV), Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598687.0605136452</v>
+        <v>598342</v>
       </c>
       <c r="R3" t="n">
-        <v>7106517.206515349</v>
+        <v>7106656</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,27 +842,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-07-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesbedömning</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,27 +872,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104159761</v>
+        <v>134039453</v>
       </c>
       <c r="B4" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +899,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörnoret, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598634.6990807866</v>
+        <v>598314</v>
       </c>
       <c r="R4" t="n">
-        <v>7106564.158463252</v>
+        <v>7106661</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +953,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,27 +983,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104159762</v>
+        <v>134036827</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,37 +1010,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörnoret, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598688.9318112903</v>
+        <v>598765</v>
       </c>
       <c r="R5" t="n">
-        <v>7106554.931663798</v>
+        <v>7106548</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,27 +1064,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,27 +1094,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104159759</v>
+        <v>134039451</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,37 +1121,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sörnoret, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598381.5225138416</v>
+        <v>598236</v>
       </c>
       <c r="R6" t="n">
-        <v>7106665.619971088</v>
+        <v>7106703</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,27 +1175,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,65 +1205,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104159758</v>
+        <v>134039460</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörnoret, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598384.644480088</v>
+        <v>598701</v>
       </c>
       <c r="R7" t="n">
-        <v>7106663.967040836</v>
+        <v>7106534</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,27 +1286,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,22 +1316,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134036820</v>
+        <v>112606430</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,42 +1343,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Sörnoret, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598471</v>
+        <v>598384</v>
       </c>
       <c r="R8" t="n">
-        <v>7106618</v>
+        <v>7106664</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,22 +1397,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:28</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:28</t>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,26 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134039452</v>
+        <v>112606436</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,37 +1445,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Sörnoret, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598299</v>
+        <v>598689</v>
       </c>
       <c r="R9" t="n">
-        <v>7106677</v>
+        <v>7106555</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,22 +1499,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,26 +1524,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134036815</v>
+        <v>7016346</v>
       </c>
       <c r="B10" t="n">
-        <v>80375</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,34 +1547,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Sörnoret (8400m SV), Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598280</v>
+        <v>598687</v>
       </c>
       <c r="R10" t="n">
-        <v>7106713</v>
+        <v>7106517</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1669,22 +1601,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:21</t>
+          <t>2013-07-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:21</t>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,71 +1620,66 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134039454</v>
+        <v>134036813</v>
       </c>
       <c r="B11" t="n">
-        <v>80481</v>
+        <v>92199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598366</v>
+        <v>598223</v>
       </c>
       <c r="R11" t="n">
-        <v>7106639</v>
+        <v>7106708</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,12 +1733,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1827,32 +1749,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134039453</v>
+        <v>134039458</v>
       </c>
       <c r="B12" t="n">
-        <v>91963</v>
+        <v>91937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598314</v>
+        <v>598655</v>
       </c>
       <c r="R12" t="n">
-        <v>7106661</v>
+        <v>7106548</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1897,7 +1819,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1829,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,32 +1860,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134039458</v>
+        <v>134039452</v>
       </c>
       <c r="B13" t="n">
-        <v>91930</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598655</v>
+        <v>598299</v>
       </c>
       <c r="R13" t="n">
-        <v>7106548</v>
+        <v>7106677</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,32 +1971,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134039460</v>
+        <v>134039455</v>
       </c>
       <c r="B14" t="n">
-        <v>91981</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598701</v>
+        <v>598368</v>
       </c>
       <c r="R14" t="n">
-        <v>7106534</v>
+        <v>7106638</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2119,7 +2041,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2051,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,32 +2082,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134039459</v>
+        <v>134039456</v>
       </c>
       <c r="B15" t="n">
-        <v>99210</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2195,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598681</v>
+        <v>598460</v>
       </c>
       <c r="R15" t="n">
-        <v>7106543</v>
+        <v>7106597</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2230,7 +2152,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2162,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134039455</v>
+        <v>112606434</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>83307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,37 +2204,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Sörnoret, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598368</v>
+        <v>598635</v>
       </c>
       <c r="R16" t="n">
-        <v>7106638</v>
+        <v>7106564</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,22 +2258,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:25</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:25</t>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,72 +2283,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134036821</v>
+        <v>134036815</v>
       </c>
       <c r="B17" t="n">
-        <v>57153</v>
+        <v>80382</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598544</v>
+        <v>598280</v>
       </c>
       <c r="R17" t="n">
-        <v>7106581</v>
+        <v>7106713</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,6 +2384,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2501,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134036824</v>
+        <v>112606432</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,45 +2418,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Sörnoret, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598638</v>
+        <v>598382</v>
       </c>
       <c r="R18" t="n">
-        <v>7106561</v>
+        <v>7106666</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2574,22 +2472,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,26 +2497,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036822</v>
+        <v>134036814</v>
       </c>
       <c r="B19" t="n">
-        <v>91987</v>
+        <v>80488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,19 +2520,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2651,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598581</v>
+        <v>598239</v>
       </c>
       <c r="R19" t="n">
-        <v>7106568</v>
+        <v>7106713</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2686,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,60 +2620,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134039457</v>
+        <v>134036819</v>
       </c>
       <c r="B20" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Namnlöstjärnen, Ås lm</t>
+          <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598464</v>
+        <v>598378</v>
       </c>
       <c r="R20" t="n">
-        <v>7106595</v>
+        <v>7106663</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2809,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2819,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,19 +2709,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2851,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134036827</v>
+        <v>134039449</v>
       </c>
       <c r="B21" t="n">
-        <v>91967</v>
+        <v>80488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,34 +2742,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Namnlöstjärn, Ås lm</t>
+          <t>Namnlöstjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598765</v>
+        <v>598236</v>
       </c>
       <c r="R21" t="n">
-        <v>7106548</v>
+        <v>7106704</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2921,7 +2801,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2931,7 +2811,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2946,12 +2826,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2962,10 +2842,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134039456</v>
+        <v>134039454</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>80488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,21 +2853,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2997,10 +2877,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598460</v>
+        <v>598366</v>
       </c>
       <c r="R22" t="n">
-        <v>7106597</v>
+        <v>7106639</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3032,7 +2912,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,7 +2922,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3073,10 +2953,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134036819</v>
+        <v>134036820</v>
       </c>
       <c r="B23" t="n">
-        <v>80481</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,37 +2964,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Namnlöstjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>598378</v>
+        <v>598471</v>
       </c>
       <c r="R23" t="n">
-        <v>7106663</v>
+        <v>7106618</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3143,7 +3028,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3153,7 +3038,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3177,6 +3062,479 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134036824</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Namnlöstjärn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>598638</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7106561</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134036821</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57153</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Namnlöstjärn, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>598544</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7106581</v>
+      </c>
+      <c r="S25" t="n">
+        <v>11</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134039457</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>598464</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7106595</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134039459</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Namnlöstjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>598681</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7106543</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>

--- a/artfynd/A 2749-2026 artfynd.xlsx
+++ b/artfynd/A 2749-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7016231</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134036816</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039453</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134036827</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039451</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039460</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606430</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606436</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7016346</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,6 +1796,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134036813</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1857,6 +1912,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039458</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039452</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2079,6 +2144,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039455</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039456</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606434</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,6 +2484,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134036815</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2506,6 +2591,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606432</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2617,6 +2707,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134036814</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2728,6 +2823,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134036819</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2839,6 +2939,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039449</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2950,6 +3055,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039454</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3066,6 +3176,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134036820</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3185,6 +3300,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134036824</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3304,6 +3424,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134036821</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3428,6 +3553,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039457</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3539,8 +3669,41 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039459</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>